--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="60">
   <si>
     <t>日期</t>
   </si>
@@ -65,28 +65,31 @@
     <t>2026-10-01</t>
   </si>
   <si>
-    <t>00:16</t>
+    <t>00:32</t>
+  </si>
+  <si>
+    <t>❌</t>
+  </si>
+  <si>
+    <t>签到失败：今天已签到，请明天再来</t>
+  </si>
+  <si>
+    <t>—</t>
   </si>
   <si>
     <t>✅</t>
   </si>
   <si>
-    <t>签到成功，获得 100 积分</t>
-  </si>
-  <si>
-    <t>已领取到家积分 5</t>
-  </si>
-  <si>
-    <t>✅ 已派</t>
-  </si>
-  <si>
-    <t>待命</t>
-  </si>
-  <si>
-    <t>10-01 04:16</t>
-  </si>
-  <si>
-    <t>已派出猫猫前往「咖啡馆」（预计 9-30 20:16 到家）</t>
+    <t>无待领取的到家积分</t>
+  </si>
+  <si>
+    <t>跳过</t>
+  </si>
+  <si>
+    <t>旅行中</t>
+  </si>
+  <si>
+    <t>猫猫正在旅行中（state=traveling），今天已派出，跳过派新行程</t>
   </si>
   <si>
     <t>正常</t>
@@ -188,7 +191,7 @@
     <t>最近更新</t>
   </si>
   <si>
-    <t>2026-10-01 00:16</t>
+    <t>2026-10-01 00:32</t>
   </si>
 </sst>
 </file>
@@ -233,7 +236,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F9FC"/>
+        <fgColor rgb="FFFDE7E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -703,46 +706,46 @@
       <c r="D2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="3">
-        <v>100</v>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="3">
-        <v>5</v>
-      </c>
-      <c r="I2" s="5">
-        <v>105</v>
+      <c r="I2" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="4">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -757,178 +760,178 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="每日记录" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="汇总" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>日期</t>
   </si>
@@ -23,18 +22,12 @@
     <t>签到</t>
   </si>
   <si>
-    <t>签到说明</t>
-  </si>
-  <si>
     <t>签到积分</t>
   </si>
   <si>
     <t>领到家积分</t>
   </si>
   <si>
-    <t>领奖说明</t>
-  </si>
-  <si>
     <t>到家积分</t>
   </si>
   <si>
@@ -44,163 +37,43 @@
     <t>派猫</t>
   </si>
   <si>
-    <t>行程状态</t>
-  </si>
-  <si>
-    <t>地点</t>
-  </si>
-  <si>
-    <t>预计到家</t>
-  </si>
-  <si>
     <t>派猫说明</t>
   </si>
   <si>
-    <t>整体</t>
-  </si>
-  <si>
     <t>模式</t>
   </si>
   <si>
     <t>2026-10-01</t>
   </si>
   <si>
-    <t>00:32</t>
-  </si>
-  <si>
-    <t>❌</t>
-  </si>
-  <si>
-    <t>签到失败：今天已签到，请明天再来</t>
-  </si>
-  <si>
-    <t>—</t>
+    <t>00:16</t>
   </si>
   <si>
     <t>✅</t>
   </si>
   <si>
-    <t>无待领取的到家积分</t>
-  </si>
-  <si>
-    <t>跳过</t>
-  </si>
-  <si>
-    <t>旅行中</t>
-  </si>
-  <si>
-    <t>猫猫正在旅行中（state=traveling），今天已派出，跳过派新行程</t>
+    <t>✅ 已派</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 9-30 20:16 到家）</t>
   </si>
   <si>
     <t>正常</t>
   </si>
   <si>
-    <t>统计区间</t>
-  </si>
-  <si>
-    <t>2026-10-01 ~ 2026-10-01</t>
-  </si>
-  <si>
-    <t>记录天数</t>
-  </si>
-  <si>
-    <t>COUNTA('每日记录'!A2:A2)</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>累计总积分</t>
   </si>
   <si>
-    <t>SUM('每日记录'!I2:I2)</t>
-  </si>
-  <si>
-    <t>日均积分</t>
-  </si>
-  <si>
-    <t>IFERROR(SUM('每日记录'!I2:I2)/COUNT('每日记录'!I2:I2),0)</t>
-  </si>
-  <si>
-    <t>签到累计积分</t>
-  </si>
-  <si>
-    <t>SUM('每日记录'!E2:E2)</t>
-  </si>
-  <si>
-    <t>到家积分累计</t>
-  </si>
-  <si>
-    <t>SUM('每日记录'!H2:H2)</t>
-  </si>
-  <si>
-    <t>单日最高积分</t>
-  </si>
-  <si>
-    <t>IFERROR(MAX('每日记录'!I2:I2),0)</t>
-  </si>
-  <si>
-    <t>签到成功天数</t>
-  </si>
-  <si>
-    <t>COUNTIF('每日记录'!C2:C2,"✅")</t>
-  </si>
-  <si>
-    <t>签到失败天数</t>
-  </si>
-  <si>
-    <t>COUNTIF('每日记录'!C2:C2,"❌")</t>
-  </si>
-  <si>
-    <t>领奖成功天数</t>
-  </si>
-  <si>
-    <t>COUNTIF('每日记录'!F2:F2,"✅")</t>
-  </si>
-  <si>
-    <t>派猫成功天数</t>
-  </si>
-  <si>
-    <t>COUNTIF('每日记录'!J2:J2,"✅ 已派")</t>
-  </si>
-  <si>
-    <t>派猫跳过天数</t>
-  </si>
-  <si>
-    <t>COUNTIF('每日记录'!J2:J2,"跳过")</t>
-  </si>
-  <si>
-    <t>派猫失败天数</t>
-  </si>
-  <si>
-    <t>COUNTIF('每日记录'!J2:J2,"❌ 失败")</t>
-  </si>
-  <si>
-    <t>整体成功天数</t>
-  </si>
-  <si>
-    <t>COUNTIF('每日记录'!O2:O2,"✅")</t>
-  </si>
-  <si>
-    <t>成功率</t>
-  </si>
-  <si>
-    <t>IFERROR(COUNTIF('每日记录'!O2:O2,"✅")/COUNTA('每日记录'!A2:A2),0)</t>
-  </si>
-  <si>
-    <t>最近更新</t>
-  </si>
-  <si>
-    <t>2026-10-01 00:32</t>
+    <t>今日已用</t>
+  </si>
+  <si>
+    <t>还剩积分</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
@@ -236,7 +109,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDE7E9"/>
+        <fgColor rgb="FFF7F9FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -272,19 +145,25 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -624,26 +503,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="40" customWidth="1"/>
-    <col min="15" max="16" width="8" customWidth="1"/>
+    <col min="9" max="9" width="52" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -674,264 +549,61 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="D2" s="2">
+        <v>100</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4">
+        <v>105</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="I2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="J2" s="5" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>33</v>
+        <v>16</v>
+      </c>
+      <c r="B4" s="7">
+        <f>SUM(G2:G2)</f>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s">
-        <v>35</v>
+        <v>17</v>
+      </c>
+      <c r="B5" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" t="s">
-        <v>59</v>
+        <v>18</v>
+      </c>
+      <c r="B6" s="8">
+        <v>1679.07</v>
       </c>
     </row>
   </sheetData>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet sheetId="1" name="每日记录" state="visible" r:id="rId4"/>
   </sheets>
@@ -43,6 +46,9 @@
     <t>模式</t>
   </si>
   <si>
+    <t>累计总积分</t>
+  </si>
+  <si>
     <t>2026-10-01</t>
   </si>
   <si>
@@ -59,9 +65,6 @@
   </si>
   <si>
     <t>正常</t>
-  </si>
-  <si>
-    <t>累计总积分</t>
   </si>
   <si>
     <t>今日已用</t>
@@ -140,10 +143,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -503,8 +509,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -516,9 +522,10 @@
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="52" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
+    <col min="11" max="12" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -549,65 +556,62 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <f>SUM(G2)</f>
+        <v>105</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2">
+      <c r="C2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3">
         <v>100</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3">
         <v>5</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="5">
         <v>105</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="J2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="8">
+        <v>25.92</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="7">
-        <f>SUM(G2:G2)</f>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="3" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="8">
-        <v>1679.07</v>
+      <c r="L3" s="9">
+        <v>1653.15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -599,15 +599,15 @@
         <v>17</v>
       </c>
       <c r="L2" s="8">
-        <v>25.92</v>
+        <v>69.6</v>
       </c>
     </row>
-    <row r="3" spans="11:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K3" s="7" t="s">
         <v>18</v>
       </c>
       <c r="L3" s="9">
-        <v>1653.15</v>
+        <v>1609.47</v>
       </c>
     </row>
   </sheetData>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -599,7 +599,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="8">
-        <v>69.6</v>
+        <v>101.17</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -607,7 +607,7 @@
         <v>18</v>
       </c>
       <c r="L3" s="9">
-        <v>1609.47</v>
+        <v>1577.9</v>
       </c>
     </row>
   </sheetData>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -599,7 +599,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="8">
-        <v>101.17</v>
+        <v>105.2</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -607,7 +607,7 @@
         <v>18</v>
       </c>
       <c r="L3" s="9">
-        <v>1577.9</v>
+        <v>1573.87</v>
       </c>
     </row>
   </sheetData>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -599,7 +599,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="8">
-        <v>105.2</v>
+        <v>118.4</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -607,7 +607,7 @@
         <v>18</v>
       </c>
       <c r="L3" s="9">
-        <v>1573.87</v>
+        <v>1560.67</v>
       </c>
     </row>
   </sheetData>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -599,7 +599,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="8">
-        <v>118.4</v>
+        <v>121.45</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -607,7 +607,7 @@
         <v>18</v>
       </c>
       <c r="L3" s="9">
-        <v>1560.67</v>
+        <v>1557.62</v>
       </c>
     </row>
   </sheetData>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -599,7 +599,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="8">
-        <v>121.45</v>
+        <v>126.25</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -607,7 +607,7 @@
         <v>18</v>
       </c>
       <c r="L3" s="9">
-        <v>1557.62</v>
+        <v>1552.82</v>
       </c>
     </row>
   </sheetData>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -52,7 +52,7 @@
     <t>2026-10-01</t>
   </si>
   <si>
-    <t>00:16</t>
+    <t>09:14</t>
   </si>
   <si>
     <t>✅</t>
@@ -143,31 +143,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -560,31 +554,30 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2)</f>
-        <v>105</v>
+        <f>SUM(G2:G2)</f>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="4">
         <v>100</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3">
-        <v>5</v>
+      <c r="F2" s="4">
+        <v>10</v>
       </c>
       <c r="G2" s="5">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>14</v>
@@ -595,19 +588,19 @@
       <c r="J2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="8">
-        <v>126.25</v>
+      <c r="L2" s="2">
+        <v>353.96</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="9">
-        <v>1552.82</v>
+      <c r="L3" s="7">
+        <v>1330.11</v>
       </c>
     </row>
   </sheetData>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>日期</t>
   </si>
@@ -68,6 +68,18 @@
   </si>
   <si>
     <t>今日已用</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>09:13</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-02 02:13 到家）</t>
   </si>
   <si>
     <t>还剩积分</t>
@@ -143,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -159,6 +171,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -554,7 +575,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G2)</f>
+        <f>SUM(G2:G3)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -592,15 +613,45 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>353.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7">
+        <v>100</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="8">
+        <v>100</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="7">
-        <v>1330.11</v>
+        <v>22</v>
+      </c>
+      <c r="L3" s="10">
+        <v>1430.11</v>
       </c>
     </row>
   </sheetData>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>日期</t>
   </si>
@@ -83,6 +83,12 @@
   </si>
   <si>
     <t>还剩积分</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-03 05:13 到家）</t>
   </si>
 </sst>
 </file>
@@ -524,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -575,7 +581,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G3)</f>
+        <f>SUM(G2:G4)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -651,7 +657,39 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>1430.11</v>
+        <v>1535.11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="4">
+        <v>100</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4">
+        <v>5</v>
+      </c>
+      <c r="G4" s="5">
+        <v>105</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
   <si>
     <t>日期</t>
   </si>
@@ -89,6 +89,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-03 05:13 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-04</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-04 08:00 到家）</t>
   </si>
 </sst>
 </file>
@@ -530,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -581,7 +590,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G4)</f>
+        <f>SUM(G2:G5)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -657,7 +666,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>1535.11</v>
+        <v>1641.11</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -689,6 +698,38 @@
         <v>24</v>
       </c>
       <c r="J4" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7">
+        <v>100</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="7">
+        <v>6</v>
+      </c>
+      <c r="G5" s="8">
+        <v>106</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
   <si>
     <t>日期</t>
   </si>
@@ -98,6 +98,12 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-04 08:00 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-05 02:14 到家）</t>
   </si>
 </sst>
 </file>
@@ -539,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -590,7 +596,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G5)</f>
+        <f>SUM(G2:G6)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -666,7 +672,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>1641.11</v>
+        <v>1747.11</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -730,6 +736,38 @@
         <v>27</v>
       </c>
       <c r="J5" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="4">
+        <v>100</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="4">
+        <v>6</v>
+      </c>
+      <c r="G6" s="5">
+        <v>106</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="32">
   <si>
     <t>日期</t>
   </si>
@@ -104,6 +104,12 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-05 02:14 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-06 05:13 到家）</t>
   </si>
 </sst>
 </file>
@@ -545,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -596,7 +602,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G6)</f>
+        <f>SUM(G2:G7)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -672,7 +678,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>1747.11</v>
+        <v>1854.11</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -768,6 +774,38 @@
         <v>29</v>
       </c>
       <c r="J6" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="7">
+        <v>100</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="7">
+        <v>7</v>
+      </c>
+      <c r="G7" s="8">
+        <v>107</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
   <si>
     <t>日期</t>
   </si>
@@ -110,6 +110,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-06 05:13 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-07 02:15 到家）</t>
   </si>
 </sst>
 </file>
@@ -551,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -602,7 +611,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G7)</f>
+        <f>SUM(G2:G8)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -678,7 +687,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>1854.11</v>
+        <v>2164.11</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -806,6 +815,38 @@
         <v>31</v>
       </c>
       <c r="J7" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="4">
+        <v>100</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="5">
+        <v>100</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
   <si>
     <t>日期</t>
   </si>
@@ -70,15 +70,15 @@
     <t>今日已用</t>
   </si>
   <si>
+    <t>—</t>
+  </si>
+  <si>
     <t>2026-10-02</t>
   </si>
   <si>
     <t>09:13</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-02 02:13 到家）</t>
   </si>
   <si>
@@ -119,6 +119,12 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-07 02:15 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-08 04:15 到家）</t>
   </si>
 </sst>
 </file>
@@ -560,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -611,7 +617,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G8)</f>
+        <f>SUM(G2:G9)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -648,28 +654,28 @@
       <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="2">
-        <v>0</v>
+      <c r="L2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7">
+        <v>100</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="7">
-        <v>100</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="G3" s="8">
         <v>100</v>
@@ -686,8 +692,8 @@
       <c r="K3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="10">
-        <v>2164.11</v>
+      <c r="L3" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -695,7 +701,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>13</v>
@@ -835,7 +841,7 @@
         <v>13</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G8" s="5">
         <v>100</v>
@@ -847,6 +853,38 @@
         <v>34</v>
       </c>
       <c r="J8" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="7">
+        <v>100</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="7">
+        <v>8</v>
+      </c>
+      <c r="G9" s="8">
+        <v>108</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="40">
   <si>
     <t>日期</t>
   </si>
@@ -70,15 +70,15 @@
     <t>今日已用</t>
   </si>
   <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>09:13</t>
+  </si>
+  <si>
     <t>—</t>
   </si>
   <si>
-    <t>2026-10-02</t>
-  </si>
-  <si>
-    <t>09:13</t>
-  </si>
-  <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-02 02:13 到家）</t>
   </si>
   <si>
@@ -125,6 +125,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-08 04:15 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>09:16</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-09 03:16 到家）</t>
   </si>
 </sst>
 </file>
@@ -566,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -617,7 +626,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G9)</f>
+        <f>SUM(G2:G10)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -654,28 +663,28 @@
       <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>18</v>
+      <c r="L2" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7">
+        <v>100</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="7">
-        <v>100</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="G3" s="8">
         <v>100</v>
@@ -692,8 +701,8 @@
       <c r="K3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="10" t="s">
-        <v>18</v>
+      <c r="L3" s="10">
+        <v>2356.24</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -701,7 +710,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>13</v>
@@ -841,7 +850,7 @@
         <v>13</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G8" s="5">
         <v>100</v>
@@ -885,6 +894,38 @@
         <v>36</v>
       </c>
       <c r="J9" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="4">
+        <v>100</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="4">
+        <v>5</v>
+      </c>
+      <c r="G10" s="5">
+        <v>105</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
   <si>
     <t>日期</t>
   </si>
@@ -134,6 +134,12 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-09 03:16 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-10 04:15 到家）</t>
   </si>
 </sst>
 </file>
@@ -575,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -626,7 +632,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G10)</f>
+        <f>SUM(G2:G11)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -664,7 +670,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>0</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -702,7 +708,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>2356.24</v>
+        <v>2461.31</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -926,6 +932,38 @@
         <v>39</v>
       </c>
       <c r="J10" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="7">
+        <v>100</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="7">
+        <v>10</v>
+      </c>
+      <c r="G11" s="8">
+        <v>110</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="44">
   <si>
     <t>日期</t>
   </si>
@@ -140,6 +140,12 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-10 04:15 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-11</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-11 03:14 到家）</t>
   </si>
 </sst>
 </file>
@@ -581,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -632,7 +638,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G11)</f>
+        <f>SUM(G2:G12)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -670,7 +676,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>4.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -708,7 +714,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>2461.31</v>
+        <v>2568.31</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -964,6 +970,38 @@
         <v>41</v>
       </c>
       <c r="J11" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="4">
+        <v>100</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="4">
+        <v>7</v>
+      </c>
+      <c r="G12" s="5">
+        <v>107</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
   <si>
     <t>日期</t>
   </si>
@@ -146,6 +146,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-11 03:14 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-12</t>
+  </si>
+  <si>
+    <t>09:18</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-12 02:18 到家）</t>
   </si>
 </sst>
 </file>
@@ -587,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -638,7 +647,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G12)</f>
+        <f>SUM(G2:G13)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -714,7 +723,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>2568.31</v>
+        <v>2677.31</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1002,6 +1011,38 @@
         <v>43</v>
       </c>
       <c r="J12" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="7">
+        <v>100</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="7">
+        <v>9</v>
+      </c>
+      <c r="G13" s="8">
+        <v>109</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="49">
   <si>
     <t>日期</t>
   </si>
@@ -155,6 +155,12 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-12 02:18 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-13</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-13 05:18 到家）</t>
   </si>
 </sst>
 </file>
@@ -596,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -647,7 +653,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G13)</f>
+        <f>SUM(G2:G14)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -723,7 +729,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>2677.31</v>
+        <v>2783.31</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1043,6 +1049,38 @@
         <v>46</v>
       </c>
       <c r="J13" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="4">
+        <v>100</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="4">
+        <v>6</v>
+      </c>
+      <c r="G14" s="5">
+        <v>106</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="52">
   <si>
     <t>日期</t>
   </si>
@@ -161,6 +161,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-13 05:18 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-14</t>
+  </si>
+  <si>
+    <t>09:28</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-14 05:28 到家）</t>
   </si>
 </sst>
 </file>
@@ -602,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -653,7 +662,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G14)</f>
+        <f>SUM(G2:G15)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -691,7 +700,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>0</v>
+        <v>32.88</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -729,7 +738,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>2783.31</v>
+        <v>2860.43</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1081,6 +1090,38 @@
         <v>48</v>
       </c>
       <c r="J14" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="7">
+        <v>100</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="7">
+        <v>10</v>
+      </c>
+      <c r="G15" s="8">
+        <v>110</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="55">
   <si>
     <t>日期</t>
   </si>
@@ -170,6 +170,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-14 05:28 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
+    <t>09:27</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-15 04:27 到家）</t>
   </si>
 </sst>
 </file>
@@ -611,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -662,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G15)</f>
+        <f>SUM(G2:G16)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -700,7 +709,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>32.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -738,7 +747,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>2860.43</v>
+        <v>2967.43</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1122,6 +1131,38 @@
         <v>51</v>
       </c>
       <c r="J15" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="4">
+        <v>100</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="4">
+        <v>7</v>
+      </c>
+      <c r="G16" s="5">
+        <v>107</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J16" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="58">
   <si>
     <t>日期</t>
   </si>
@@ -179,6 +179,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-15 04:27 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>09:26</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-16 05:26 到家）</t>
   </si>
 </sst>
 </file>
@@ -620,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -671,7 +680,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G16)</f>
+        <f>SUM(G2:G17)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -747,7 +756,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>2967.43</v>
+        <v>3076.43</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1163,6 +1172,38 @@
         <v>54</v>
       </c>
       <c r="J16" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="7">
+        <v>100</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="7">
+        <v>9</v>
+      </c>
+      <c r="G17" s="8">
+        <v>109</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="60">
   <si>
     <t>日期</t>
   </si>
@@ -188,6 +188,12 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-16 05:26 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-17</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-17 03:27 到家）</t>
   </si>
 </sst>
 </file>
@@ -629,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -680,7 +686,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G17)</f>
+        <f>SUM(G2:G18)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -756,7 +762,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>3076.43</v>
+        <v>3682.43</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1204,6 +1210,38 @@
         <v>57</v>
       </c>
       <c r="J17" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="4">
+        <v>100</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="5">
+        <v>100</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="62">
   <si>
     <t>日期</t>
   </si>
@@ -194,6 +194,12 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-17 03:27 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-18</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-18 04:27 到家）</t>
   </si>
 </sst>
 </file>
@@ -635,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -686,7 +692,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G18)</f>
+        <f>SUM(G2:G19)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -762,7 +768,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>3682.43</v>
+        <v>3792.43</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1242,6 +1248,38 @@
         <v>59</v>
       </c>
       <c r="J18" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="7">
+        <v>100</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="7">
+        <v>10</v>
+      </c>
+      <c r="G19" s="8">
+        <v>110</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
   <si>
     <t>日期</t>
   </si>
@@ -200,6 +200,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-18 04:27 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-19</t>
+  </si>
+  <si>
+    <t>09:31</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-19 03:31 到家）</t>
   </si>
 </sst>
 </file>
@@ -641,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -692,7 +701,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G19)</f>
+        <f>SUM(G2:G20)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -768,7 +777,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>3792.43</v>
+        <v>3901.43</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1280,6 +1289,38 @@
         <v>61</v>
       </c>
       <c r="J19" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="4">
+        <v>100</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="4">
+        <v>9</v>
+      </c>
+      <c r="G20" s="5">
+        <v>109</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
   <si>
     <t>日期</t>
   </si>
@@ -209,6 +209,12 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-19 03:31 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-20 02:30 到家）</t>
   </si>
 </sst>
 </file>
@@ -650,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -701,7 +707,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G20)</f>
+        <f>SUM(G2:G21)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -777,7 +783,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>3901.43</v>
+        <v>4010.43</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1321,6 +1327,38 @@
         <v>64</v>
       </c>
       <c r="J20" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="7">
+        <v>100</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="7">
+        <v>9</v>
+      </c>
+      <c r="G21" s="8">
+        <v>109</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="69">
   <si>
     <t>日期</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-20 02:30 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-21</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-21 05:31 到家）</t>
   </si>
 </sst>
 </file>
@@ -656,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -707,7 +713,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G21)</f>
+        <f>SUM(G2:G22)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -745,7 +751,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>0</v>
+        <v>1197.07</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -783,7 +789,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>4010.43</v>
+        <v>2918.36</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1359,6 +1365,38 @@
         <v>66</v>
       </c>
       <c r="J21" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="4">
+        <v>100</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="4">
+        <v>5</v>
+      </c>
+      <c r="G22" s="5">
+        <v>105</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="72">
   <si>
     <t>日期</t>
   </si>
@@ -221,6 +221,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-21 05:31 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-22</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-22 02:30 到家）</t>
   </si>
 </sst>
 </file>
@@ -662,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -713,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G22)</f>
+        <f>SUM(G2:G23)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -751,7 +760,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>1197.07</v>
+        <v>352.55</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -789,7 +798,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>2918.36</v>
+        <v>2670.81</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1397,6 +1406,38 @@
         <v>68</v>
       </c>
       <c r="J22" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="7">
+        <v>100</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="7">
+        <v>5</v>
+      </c>
+      <c r="G23" s="8">
+        <v>105</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="75">
   <si>
     <t>日期</t>
   </si>
@@ -230,6 +230,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-22 02:30 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-23</t>
+  </si>
+  <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-23 02:34 到家）</t>
   </si>
 </sst>
 </file>
@@ -671,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -722,7 +731,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G23)</f>
+        <f>SUM(G2:G24)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -760,7 +769,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>352.55</v>
+        <v>359.41</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -798,7 +807,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>2670.81</v>
+        <v>2417.4</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1438,6 +1447,38 @@
         <v>71</v>
       </c>
       <c r="J23" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="4">
+        <v>100</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="4">
+        <v>6</v>
+      </c>
+      <c r="G24" s="5">
+        <v>106</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J24" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="78">
   <si>
     <t>日期</t>
   </si>
@@ -239,6 +239,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-23 02:34 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-24</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-24 02:35 到家）</t>
   </si>
 </sst>
 </file>
@@ -680,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -731,7 +740,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G24)</f>
+        <f>SUM(G2:G25)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -769,7 +778,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>359.41</v>
+        <v>312.97</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -807,7 +816,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>2417.4</v>
+        <v>2214.43</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1479,6 +1488,38 @@
         <v>74</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="7">
+        <v>100</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="7">
+        <v>10</v>
+      </c>
+      <c r="G25" s="8">
+        <v>110</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="80">
   <si>
     <t>日期</t>
   </si>
@@ -248,6 +248,12 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-24 02:35 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-25</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-25 04:27 到家）</t>
   </si>
 </sst>
 </file>
@@ -689,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -740,7 +746,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G25)</f>
+        <f>SUM(G2:G26)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -778,7 +784,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>312.97</v>
+        <v>246.53</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -816,7 +822,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>2214.43</v>
+        <v>2074.9</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1520,6 +1526,38 @@
         <v>77</v>
       </c>
       <c r="J25" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="4">
+        <v>100</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="4">
+        <v>7</v>
+      </c>
+      <c r="G26" s="5">
+        <v>107</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="83">
   <si>
     <t>日期</t>
   </si>
@@ -254,6 +254,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-25 04:27 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-26</t>
+  </si>
+  <si>
+    <t>09:39</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-26 05:39 到家）</t>
   </si>
 </sst>
 </file>
@@ -695,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -746,7 +755,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G26)</f>
+        <f>SUM(G2:G27)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -784,7 +793,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>246.53</v>
+        <v>513.24</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -822,7 +831,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>2074.9</v>
+        <v>1669.66</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1558,6 +1567,38 @@
         <v>79</v>
       </c>
       <c r="J26" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="7">
+        <v>100</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="7">
+        <v>8</v>
+      </c>
+      <c r="G27" s="8">
+        <v>108</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="86">
   <si>
     <t>日期</t>
   </si>
@@ -263,6 +263,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-26 05:39 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-27</t>
+  </si>
+  <si>
+    <t>09:37</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-27 02:37 到家）</t>
   </si>
 </sst>
 </file>
@@ -704,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -755,7 +764,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G27)</f>
+        <f>SUM(G2:G28)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -793,7 +802,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>513.24</v>
+        <v>133.72</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -831,7 +840,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>1669.66</v>
+        <v>1643.94</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1599,6 +1608,38 @@
         <v>82</v>
       </c>
       <c r="J27" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="4">
+        <v>100</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="4">
+        <v>8</v>
+      </c>
+      <c r="G28" s="5">
+        <v>108</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J28" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="89">
   <si>
     <t>日期</t>
   </si>
@@ -272,6 +272,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-27 02:37 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-28</t>
+  </si>
+  <si>
+    <t>09:48</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-28 02:48 到家）</t>
   </si>
 </sst>
 </file>
@@ -713,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -764,7 +773,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G28)</f>
+        <f>SUM(G2:G29)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -802,7 +811,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>133.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -840,7 +849,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>1643.94</v>
+        <v>1749.94</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1640,6 +1649,38 @@
         <v>85</v>
       </c>
       <c r="J28" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="7">
+        <v>100</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="7">
+        <v>6</v>
+      </c>
+      <c r="G29" s="8">
+        <v>106</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
   <si>
     <t>日期</t>
   </si>
@@ -281,6 +281,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-28 02:48 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-29</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-29 03:50 到家）</t>
   </si>
 </sst>
 </file>
@@ -722,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -773,7 +782,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G29)</f>
+        <f>SUM(G2:G30)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -811,7 +820,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>0</v>
+        <v>55.34</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -849,7 +858,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>1749.94</v>
+        <v>1804.6</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1681,6 +1690,38 @@
         <v>88</v>
       </c>
       <c r="J29" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="4">
+        <v>100</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="4">
+        <v>10</v>
+      </c>
+      <c r="G30" s="5">
+        <v>110</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J30" s="6" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="95">
   <si>
     <t>日期</t>
   </si>
@@ -290,6 +290,15 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-29 03:50 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-30</t>
+  </si>
+  <si>
+    <t>09:51</t>
+  </si>
+  <si>
+    <t>已派出猫猫前往「咖啡馆」（预计 10-30 03:51 到家）</t>
   </si>
 </sst>
 </file>
@@ -731,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -782,7 +791,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G30)</f>
+        <f>SUM(G2:G31)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -820,7 +829,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="2">
-        <v>55.34</v>
+        <v>73.88</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -858,7 +867,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="10">
-        <v>1804.6</v>
+        <v>1836.72</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1722,6 +1731,38 @@
         <v>91</v>
       </c>
       <c r="J30" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="7">
+        <v>100</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="7">
+        <v>6</v>
+      </c>
+      <c r="G31" s="8">
+        <v>106</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="J31" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/history/buddy-ledger.xlsx
+++ b/history/buddy-ledger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="99">
   <si>
     <t>日期</t>
   </si>
@@ -70,15 +70,15 @@
     <t>今日已用</t>
   </si>
   <si>
+    <t>—</t>
+  </si>
+  <si>
     <t>2026-10-02</t>
   </si>
   <si>
     <t>09:13</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-02 02:13 到家）</t>
   </si>
   <si>
@@ -299,6 +299,18 @@
   </si>
   <si>
     <t>已派出猫猫前往「咖啡馆」（预计 10-30 03:51 到家）</t>
+  </si>
+  <si>
+    <t>2026-10-31</t>
+  </si>
+  <si>
+    <t>❌</t>
+  </si>
+  <si>
+    <t>跳过</t>
+  </si>
+  <si>
+    <t>行程状态查询失败：HTTP 401</t>
   </si>
 </sst>
 </file>
@@ -326,7 +338,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,6 +353,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F9FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE7E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -371,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -399,6 +416,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -740,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -791,7 +818,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="2">
-        <f>SUM(G2:G31)</f>
+        <f>SUM(G2:G32)</f>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -828,28 +855,28 @@
       <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="2">
-        <v>73.88</v>
+      <c r="L2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7">
+        <v>100</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="7">
-        <v>100</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="G3" s="8">
         <v>100</v>
@@ -866,8 +893,8 @@
       <c r="K3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="10">
-        <v>1836.72</v>
+      <c r="L3" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -875,7 +902,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>13</v>
@@ -1015,7 +1042,7 @@
         <v>13</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G8" s="5">
         <v>100</v>
@@ -1335,7 +1362,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G18" s="5">
         <v>100</v>
@@ -1763,6 +1790,38 @@
         <v>94</v>
       </c>
       <c r="J31" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="J32" s="14" t="s">
         <v>16</v>
       </c>
     </row>
